--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_LUJISA GUADALAJARA BASKET.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_LUJISA GUADALAJARA BASKET.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>B. OJEDA OCHOA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>43.6641</v>
+        <v>35.3306</v>
       </c>
       <c r="E2" t="n">
-        <v>46.0567</v>
+        <v>38.4649</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.3928</v>
+        <v>-3.1342</v>
       </c>
       <c r="G2" t="n">
-        <v>10.7342</v>
+        <v>29.7764</v>
       </c>
       <c r="H2" t="n">
-        <v>22.375</v>
+        <v>7.6792</v>
       </c>
       <c r="I2" t="n">
-        <v>-11.6403</v>
+        <v>22.0972</v>
       </c>
       <c r="J2" t="n">
-        <v>48.1186</v>
+        <v>62.3005</v>
       </c>
       <c r="K2" t="n">
-        <v>39.1591</v>
+        <v>25.4044</v>
       </c>
       <c r="L2" t="n">
-        <v>8.959099999999999</v>
+        <v>36.8964</v>
       </c>
       <c r="M2" t="n">
-        <v>-37.3836</v>
+        <v>-32.5241</v>
       </c>
       <c r="N2" t="n">
-        <v>-16.7844</v>
+        <v>-17.7252</v>
       </c>
       <c r="O2" t="n">
-        <v>-20.5997</v>
+        <v>-14.7991</v>
       </c>
       <c r="P2" t="n">
-        <v>-18.2391</v>
+        <v>-7.179</v>
       </c>
       <c r="Q2" t="n">
-        <v>-64.6129</v>
+        <v>-47.7319</v>
       </c>
       <c r="R2" t="n">
-        <v>46.374</v>
+        <v>40.5528</v>
       </c>
       <c r="S2" t="n">
-        <v>41.5434</v>
+        <v>-1.4606</v>
       </c>
       <c r="T2" t="n">
-        <v>28.2965</v>
+        <v>-3.3977</v>
       </c>
       <c r="U2" t="n">
-        <v>13.2469</v>
+        <v>1.9368</v>
       </c>
       <c r="V2" t="n">
-        <v>9.625399999999999</v>
+        <v>14.1943</v>
       </c>
       <c r="W2" t="n">
-        <v>34.2546</v>
+        <v>27.2936</v>
       </c>
       <c r="X2" t="n">
-        <v>-24.6297</v>
+        <v>-13.0997</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. OJEDA OCHOA</t>
+          <t>L. VALERA VILLEGAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>20.4603</v>
+        <v>22.9988</v>
       </c>
       <c r="E3" t="n">
-        <v>28.3548</v>
+        <v>36.6127</v>
       </c>
       <c r="F3" t="n">
-        <v>-7.8944</v>
+        <v>-13.6138</v>
       </c>
       <c r="G3" t="n">
-        <v>29.7764</v>
+        <v>-2.371899999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>7.6792</v>
+        <v>10.7799</v>
       </c>
       <c r="I3" t="n">
-        <v>22.0972</v>
+        <v>-13.1516</v>
       </c>
       <c r="J3" t="n">
-        <v>62.3005</v>
+        <v>36.0942</v>
       </c>
       <c r="K3" t="n">
-        <v>25.4044</v>
+        <v>30.2696</v>
       </c>
       <c r="L3" t="n">
-        <v>36.8964</v>
+        <v>5.8243</v>
       </c>
       <c r="M3" t="n">
-        <v>-32.5241</v>
+        <v>-38.4657</v>
       </c>
       <c r="N3" t="n">
-        <v>-17.7252</v>
+        <v>-19.4901</v>
       </c>
       <c r="O3" t="n">
-        <v>-14.7991</v>
+        <v>-18.9756</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.179</v>
+        <v>0.388</v>
       </c>
       <c r="Q3" t="n">
-        <v>-47.7319</v>
+        <v>-47.7321</v>
       </c>
       <c r="R3" t="n">
-        <v>40.5528</v>
+        <v>48.1201</v>
       </c>
       <c r="S3" t="n">
-        <v>-16.331</v>
+        <v>4.0095</v>
       </c>
       <c r="T3" t="n">
-        <v>-13.5078</v>
+        <v>-1.2594</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.8234</v>
+        <v>5.2691</v>
       </c>
       <c r="V3" t="n">
-        <v>14.1943</v>
+        <v>20.973</v>
       </c>
       <c r="W3" t="n">
-        <v>27.2936</v>
+        <v>49.5099</v>
       </c>
       <c r="X3" t="n">
-        <v>-13.0997</v>
+        <v>-28.5369</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. VALERA VILLEGAS</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>17.0687</v>
+        <v>21.2511</v>
       </c>
       <c r="E4" t="n">
-        <v>32.7088</v>
+        <v>27.7384</v>
       </c>
       <c r="F4" t="n">
-        <v>-15.6401</v>
+        <v>-6.4875</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.371899999999999</v>
+        <v>10.7342</v>
       </c>
       <c r="H4" t="n">
-        <v>10.7799</v>
+        <v>22.375</v>
       </c>
       <c r="I4" t="n">
-        <v>-13.1516</v>
+        <v>-11.6403</v>
       </c>
       <c r="J4" t="n">
-        <v>36.0942</v>
+        <v>48.1186</v>
       </c>
       <c r="K4" t="n">
-        <v>30.2696</v>
+        <v>39.1591</v>
       </c>
       <c r="L4" t="n">
-        <v>5.8243</v>
+        <v>8.959099999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-38.4657</v>
+        <v>-37.3836</v>
       </c>
       <c r="N4" t="n">
-        <v>-19.4901</v>
+        <v>-16.7844</v>
       </c>
       <c r="O4" t="n">
-        <v>-18.9756</v>
+        <v>-20.5997</v>
       </c>
       <c r="P4" t="n">
-        <v>0.388</v>
+        <v>-18.2391</v>
       </c>
       <c r="Q4" t="n">
-        <v>-47.7321</v>
+        <v>-64.6129</v>
       </c>
       <c r="R4" t="n">
-        <v>48.1201</v>
+        <v>46.374</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.9208</v>
+        <v>19.1304</v>
       </c>
       <c r="T4" t="n">
-        <v>-5.1633</v>
+        <v>9.978300000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>3.2423</v>
+        <v>9.1523</v>
       </c>
       <c r="V4" t="n">
-        <v>20.973</v>
+        <v>9.625399999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>49.5099</v>
+        <v>34.2546</v>
       </c>
       <c r="X4" t="n">
-        <v>-28.5369</v>
+        <v>-24.6297</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>14.3802</v>
+        <v>0.4461999999999996</v>
       </c>
       <c r="E5" t="n">
-        <v>16.6567</v>
+        <v>5.745799999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.2762</v>
+        <v>-5.2996</v>
       </c>
       <c r="G5" t="n">
         <v>0.8595999999999975</v>
@@ -844,13 +844,13 @@
         <v>34.9262</v>
       </c>
       <c r="S5" t="n">
-        <v>18.3053</v>
+        <v>4.3711</v>
       </c>
       <c r="T5" t="n">
-        <v>11.9946</v>
+        <v>1.0837</v>
       </c>
       <c r="U5" t="n">
-        <v>6.310700000000001</v>
+        <v>3.2875</v>
       </c>
       <c r="V5" t="n">
         <v>-4.9788</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. BUSTOS NGUEMA</t>
+          <t>M. RODRIGUEZ MORENO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7228</v>
+        <v>-2.8136</v>
       </c>
       <c r="E8" t="n">
-        <v>1.472100000000001</v>
+        <v>-2.7685</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.195</v>
+        <v>-0.04519999999999995</v>
       </c>
       <c r="G8" t="n">
-        <v>-10.6608</v>
+        <v>-3.5415</v>
       </c>
       <c r="H8" t="n">
-        <v>-11.8091</v>
+        <v>-2.1207</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1485</v>
+        <v>-1.4209</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4500999999999999</v>
+        <v>-2.2604</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.6464</v>
+        <v>-1.1286</v>
       </c>
       <c r="L8" t="n">
-        <v>4.196300000000001</v>
+        <v>-1.1316</v>
       </c>
       <c r="M8" t="n">
-        <v>-10.2109</v>
+        <v>-1.2813</v>
       </c>
       <c r="N8" t="n">
-        <v>-7.1628</v>
+        <v>-0.9918999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.047899999999999</v>
+        <v>-0.2891</v>
       </c>
       <c r="P8" t="n">
-        <v>4.4628</v>
+        <v>0.194</v>
       </c>
       <c r="Q8" t="n">
-        <v>-14.9405</v>
+        <v>-0.9702</v>
       </c>
       <c r="R8" t="n">
-        <v>19.4033</v>
+        <v>1.1642</v>
       </c>
       <c r="S8" t="n">
-        <v>6.5453</v>
+        <v>0.5339</v>
       </c>
       <c r="T8" t="n">
-        <v>4.7723</v>
+        <v>0.462</v>
       </c>
       <c r="U8" t="n">
-        <v>1.7736</v>
+        <v>0.07180000000000002</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.0702</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>12.0909</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-14.1611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3659</v>
+        <v>-2.8808</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2919</v>
+        <v>-1.6923</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.074</v>
+        <v>-1.1887</v>
       </c>
       <c r="G9" t="n">
         <v>-2.7081</v>
@@ -1156,13 +1156,13 @@
         <v>2.7164</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4301</v>
+        <v>0.9152</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3048999999999999</v>
+        <v>-0.09549999999999995</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1252</v>
+        <v>1.0105</v>
       </c>
       <c r="V9" t="n">
         <v>-0.894</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ MORENO</t>
+          <t>J. BUSTOS NGUEMA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.541</v>
+        <v>-3.8613</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1689</v>
+        <v>-1.3306</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3722</v>
+        <v>-2.5307</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.5415</v>
+        <v>-10.6608</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.1207</v>
+        <v>-11.8091</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4209</v>
+        <v>1.1485</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.2604</v>
+        <v>-0.4500999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1286</v>
+        <v>-4.6464</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1316</v>
+        <v>4.196300000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2813</v>
+        <v>-10.2109</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9918999999999999</v>
+        <v>-7.1628</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2891</v>
+        <v>-3.047899999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>0.194</v>
+        <v>4.4628</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9702</v>
+        <v>-14.9405</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1642</v>
+        <v>19.4033</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1936</v>
+        <v>4.4071</v>
       </c>
       <c r="T10" t="n">
-        <v>0.06160000000000003</v>
+        <v>1.9695</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2552</v>
+        <v>2.4381</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-2.0702</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>12.0909</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-14.1611</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. ALMENARA SANABRIAS</t>
+          <t>A. ARMSTRONG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>-13.1228</v>
+        <v>-6.039799999999998</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.381399999999999</v>
+        <v>0.08139999999999969</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.7416</v>
+        <v>-6.121200000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.4437</v>
+        <v>12.7534</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.5667</v>
+        <v>7.9511</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1228000000000004</v>
+        <v>4.802099999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>2.556</v>
+        <v>49.2615</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7702000000000001</v>
+        <v>25.0833</v>
       </c>
       <c r="L11" t="n">
-        <v>3.3263</v>
+        <v>24.1782</v>
       </c>
       <c r="M11" t="n">
-        <v>-6.9998</v>
+        <v>-36.5083</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.7963</v>
+        <v>-17.1321</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.2034</v>
+        <v>-19.3762</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.2388</v>
+        <v>-4.850699999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-11.4479</v>
+        <v>-53.553</v>
       </c>
       <c r="R11" t="n">
-        <v>6.209</v>
+        <v>48.7021</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.0853</v>
+        <v>-2.9052</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.9955</v>
+        <v>-2.4978</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0898</v>
+        <v>-0.4076000000000002</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.3549</v>
+        <v>-11.0372</v>
       </c>
       <c r="W11" t="n">
-        <v>1.506</v>
+        <v>6.8701</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.8609</v>
+        <v>-17.9073</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>-16.0518</v>
+        <v>-10.1688</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.530899999999999</v>
+        <v>-0.2285999999999994</v>
       </c>
       <c r="F12" t="n">
-        <v>-13.5207</v>
+        <v>-9.940000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-10.1363</v>
@@ -1390,13 +1390,13 @@
         <v>18.6271</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.9919</v>
+        <v>-2.1088</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.4882</v>
+        <v>-1.1859</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.5034</v>
+        <v>-0.9226</v>
       </c>
       <c r="V12" t="n">
         <v>-4.132400000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. HOYA MARTINEZ</t>
+          <t>D. ALMENARA SANABRIAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>-18.1107</v>
+        <v>-11.5344</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.6864</v>
+        <v>-8.5806</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.4244</v>
+        <v>-2.954</v>
       </c>
       <c r="G13" t="n">
-        <v>-12.95</v>
+        <v>-4.4437</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.7184</v>
+        <v>-4.5667</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.2319</v>
+        <v>0.1228000000000004</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2235</v>
+        <v>2.556</v>
       </c>
       <c r="K13" t="n">
-        <v>5.7714</v>
+        <v>-0.7702000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.5476</v>
+        <v>3.3263</v>
       </c>
       <c r="M13" t="n">
-        <v>-16.1736</v>
+        <v>-6.9998</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.4898</v>
+        <v>-3.7963</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.6838</v>
+        <v>-3.2034</v>
       </c>
       <c r="P13" t="n">
-        <v>9.3133</v>
+        <v>-5.2388</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.4631</v>
+        <v>-11.4479</v>
       </c>
       <c r="R13" t="n">
-        <v>26.7764</v>
+        <v>6.209</v>
       </c>
       <c r="S13" t="n">
-        <v>8.5403</v>
+        <v>-0.4967</v>
       </c>
       <c r="T13" t="n">
-        <v>6.4722</v>
+        <v>-1.1947</v>
       </c>
       <c r="U13" t="n">
-        <v>2.0679</v>
+        <v>0.6977</v>
       </c>
       <c r="V13" t="n">
-        <v>-23.0147</v>
+        <v>-1.3549</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0806</v>
+        <v>1.506</v>
       </c>
       <c r="X13" t="n">
-        <v>-24.0953</v>
+        <v>-2.8609</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. EBOLO OLU-ELIJAH</t>
+          <t>E. CALVO SALVE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>-20.4828</v>
+        <v>-14.4603</v>
       </c>
       <c r="E14" t="n">
-        <v>-25.241</v>
+        <v>-8.471700000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>4.7579</v>
+        <v>-5.9886</v>
       </c>
       <c r="G14" t="n">
-        <v>-17.2205</v>
+        <v>-1.0283</v>
       </c>
       <c r="H14" t="n">
-        <v>-9.615200000000002</v>
+        <v>2.4889</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.605400000000001</v>
+        <v>-3.5173</v>
       </c>
       <c r="J14" t="n">
-        <v>20.3551</v>
+        <v>29.3711</v>
       </c>
       <c r="K14" t="n">
-        <v>7.9057</v>
+        <v>20.4526</v>
       </c>
       <c r="L14" t="n">
-        <v>12.4494</v>
+        <v>8.918200000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-37.5754</v>
+        <v>-30.3996</v>
       </c>
       <c r="N14" t="n">
-        <v>-17.521</v>
+        <v>-17.964</v>
       </c>
       <c r="O14" t="n">
-        <v>-20.0548</v>
+        <v>-12.4354</v>
       </c>
       <c r="P14" t="n">
-        <v>-6.2093</v>
+        <v>-9.313599999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-55.49319999999999</v>
+        <v>-41.5228</v>
       </c>
       <c r="R14" t="n">
-        <v>49.2844</v>
+        <v>32.2095</v>
       </c>
       <c r="S14" t="n">
-        <v>6.6063</v>
+        <v>-1.7618</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.350100000000001</v>
+        <v>-3.984</v>
       </c>
       <c r="U14" t="n">
-        <v>10.9566</v>
+        <v>2.2222</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.6599</v>
+        <v>-2.356699999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>14.2475</v>
+        <v>7.664000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-17.9073</v>
+        <v>-10.0207</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. CALVO SALVE</t>
+          <t>J. HOYA MARTINEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>-21.0062</v>
+        <v>-18.9164</v>
       </c>
       <c r="E15" t="n">
-        <v>-12.1753</v>
+        <v>-8.788499999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.8306</v>
+        <v>-10.1276</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.0283</v>
+        <v>-12.95</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4889</v>
+        <v>-4.7184</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.5173</v>
+        <v>-8.2319</v>
       </c>
       <c r="J15" t="n">
-        <v>29.3711</v>
+        <v>3.2235</v>
       </c>
       <c r="K15" t="n">
-        <v>20.4526</v>
+        <v>5.7714</v>
       </c>
       <c r="L15" t="n">
-        <v>8.918200000000001</v>
+        <v>-2.5476</v>
       </c>
       <c r="M15" t="n">
-        <v>-30.3996</v>
+        <v>-16.1736</v>
       </c>
       <c r="N15" t="n">
-        <v>-17.964</v>
+        <v>-10.4898</v>
       </c>
       <c r="O15" t="n">
-        <v>-12.4354</v>
+        <v>-5.6838</v>
       </c>
       <c r="P15" t="n">
-        <v>-9.313599999999999</v>
+        <v>9.3133</v>
       </c>
       <c r="Q15" t="n">
-        <v>-41.5228</v>
+        <v>-17.4631</v>
       </c>
       <c r="R15" t="n">
-        <v>32.2095</v>
+        <v>26.7764</v>
       </c>
       <c r="S15" t="n">
-        <v>-8.307499999999999</v>
+        <v>7.7352</v>
       </c>
       <c r="T15" t="n">
-        <v>-7.6877</v>
+        <v>4.3701</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6198000000000001</v>
+        <v>3.3648</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.356699999999999</v>
+        <v>-23.0147</v>
       </c>
       <c r="W15" t="n">
-        <v>7.664000000000001</v>
+        <v>1.0806</v>
       </c>
       <c r="X15" t="n">
-        <v>-10.0207</v>
+        <v>-24.0953</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ARMSTRONG</t>
+          <t>D. EBOLO OLU-ELIJAH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-24.2159</v>
+        <v>-20.3401</v>
       </c>
       <c r="E16" t="n">
-        <v>-10.6293</v>
+        <v>-22.6384</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.5867</v>
+        <v>2.298399999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>12.7534</v>
+        <v>-17.2205</v>
       </c>
       <c r="H16" t="n">
-        <v>7.9511</v>
+        <v>-9.615200000000002</v>
       </c>
       <c r="I16" t="n">
-        <v>4.802099999999999</v>
+        <v>-7.605400000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>49.2615</v>
+        <v>20.3551</v>
       </c>
       <c r="K16" t="n">
-        <v>25.0833</v>
+        <v>7.9057</v>
       </c>
       <c r="L16" t="n">
-        <v>24.1782</v>
+        <v>12.4494</v>
       </c>
       <c r="M16" t="n">
-        <v>-36.5083</v>
+        <v>-37.5754</v>
       </c>
       <c r="N16" t="n">
-        <v>-17.1321</v>
+        <v>-17.521</v>
       </c>
       <c r="O16" t="n">
-        <v>-19.3762</v>
+        <v>-20.0548</v>
       </c>
       <c r="P16" t="n">
-        <v>-4.850699999999999</v>
+        <v>-6.2093</v>
       </c>
       <c r="Q16" t="n">
-        <v>-53.553</v>
+        <v>-55.49319999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>48.7021</v>
+        <v>49.2844</v>
       </c>
       <c r="S16" t="n">
-        <v>-21.0812</v>
+        <v>6.7493</v>
       </c>
       <c r="T16" t="n">
-        <v>-13.2085</v>
+        <v>-1.7475</v>
       </c>
       <c r="U16" t="n">
-        <v>-7.8732</v>
+        <v>8.4971</v>
       </c>
       <c r="V16" t="n">
-        <v>-11.0372</v>
+        <v>-3.6599</v>
       </c>
       <c r="W16" t="n">
-        <v>6.8701</v>
+        <v>14.2475</v>
       </c>
       <c r="X16" t="n">
         <v>-17.9073</v>
@@ -1735,19 +1735,19 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-26.5713</v>
+        <v>-12.51349999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>53.25500000000002</v>
+        <v>53.25499999999998</v>
       </c>
       <c r="F17" t="n">
-        <v>-79.82659999999998</v>
+        <v>-65.7685</v>
       </c>
       <c r="G17" t="n">
-        <v>-12.28060000000001</v>
+        <v>-12.2806</v>
       </c>
       <c r="H17" t="n">
-        <v>7.712200000000001</v>
+        <v>7.712199999999992</v>
       </c>
       <c r="I17" t="n">
         <v>-19.9927</v>
@@ -1771,7 +1771,7 @@
         <v>-135.7555</v>
       </c>
       <c r="P17" t="n">
-        <v>-30.0756</v>
+        <v>-30.07560000000001</v>
       </c>
       <c r="Q17" t="n">
         <v>-405.5283</v>
@@ -1780,16 +1780,16 @@
         <v>375.4535</v>
       </c>
       <c r="S17" t="n">
-        <v>24.4897</v>
+        <v>38.5489</v>
       </c>
       <c r="T17" t="n">
-        <v>2.198099999999997</v>
+        <v>2.198200000000003</v>
       </c>
       <c r="U17" t="n">
-        <v>22.2914</v>
+        <v>36.3507</v>
       </c>
       <c r="V17" t="n">
-        <v>-8.706099999999996</v>
+        <v>-8.706100000000003</v>
       </c>
       <c r="W17" t="n">
         <v>171.8814</v>
